--- a/Data/testing01.xlsx
+++ b/Data/testing01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kinghoisiu/Desktop/Project/spark-housing/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GithubRepo\spark-housing\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916DCA7E-39B5-C447-B011-22487F604EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932EF02E-556B-4C17-A47D-9621A3B31617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{8943A59D-5F50-1846-AE94-00FE3EDCC890}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8943A59D-5F50-1846-AE94-00FE3EDCC890}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -47,12 +47,6 @@
     <t>Class A Kowloon - Remarks</t>
   </si>
   <si>
-    <t>Class A New Kowloom</t>
-  </si>
-  <si>
-    <t>Class A New Kowloom - Remarks</t>
-  </si>
-  <si>
     <t>Class A New Territories</t>
   </si>
   <si>
@@ -264,17 +258,25 @@
   </si>
   <si>
     <t>Class A Hong Kong Remarks</t>
+  </si>
+  <si>
+    <t>Class A New Kowloon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class A New Kowloon - Remarks</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -296,6 +298,13 @@
       <color theme="1"/>
       <name val="Helvetica"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -325,7 +334,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -341,7 +350,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -658,23 +667,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{432F1D3C-21E5-914A-A533-F56C539E8734}">
   <dimension ref="A1:AO34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.1640625" customWidth="1"/>
+    <col min="4" max="4" width="14.125" customWidth="1"/>
     <col min="5" max="5" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.125" customWidth="1"/>
+    <col min="7" max="7" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:41">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -683,117 +694,117 @@
         <v>2</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AN1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AO1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AN1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:41">
+      <c r="A2" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="AO1" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="B2" s="2">
         <v>78.5</v>
@@ -839,13 +850,13 @@
         <v>61.3</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="X2" s="2">
         <v>57.5</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z2" s="2">
         <v>108.5</v>
@@ -855,19 +866,19 @@
         <v>100.5</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AD2" s="2">
         <v>89.4</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF2" s="2">
         <v>76.2</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH2" s="2">
         <v>122.7</v>
@@ -877,22 +888,22 @@
         <v>135.5</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AM2" s="3"/>
       <c r="AN2" s="2">
         <v>68.5</v>
       </c>
       <c r="AO2" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41">
+      <c r="A3" s="1" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="B3" s="2">
         <v>80.2</v>
@@ -942,7 +953,7 @@
         <v>39.5</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z3" s="2">
         <v>106.7</v>
@@ -956,7 +967,7 @@
         <v>86.6</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF3" s="2">
         <v>68.3</v>
@@ -970,24 +981,24 @@
         <v>68.2</v>
       </c>
       <c r="AK3" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL3" s="2">
         <v>74.099999999999994</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN3" s="2">
         <v>76.099999999999994</v>
       </c>
       <c r="AO3" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:41">
       <c r="A4" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2">
         <v>76</v>
@@ -1053,7 +1064,7 @@
         <v>75</v>
       </c>
       <c r="AG4" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH4" s="2">
         <v>122.6</v>
@@ -1063,24 +1074,24 @@
         <v>68.3</v>
       </c>
       <c r="AK4" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL4" s="2">
         <v>74.099999999999994</v>
       </c>
       <c r="AM4" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN4" s="2">
         <v>68.400000000000006</v>
       </c>
       <c r="AO4" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2">
         <v>77.7</v>
@@ -1142,13 +1153,13 @@
         <v>84</v>
       </c>
       <c r="AE5" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF5" s="2">
         <v>76</v>
       </c>
       <c r="AG5" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH5" s="2">
         <v>106.2</v>
@@ -1158,24 +1169,24 @@
         <v>98.6</v>
       </c>
       <c r="AK5" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL5" s="2">
         <v>57.7</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN5" s="2">
         <v>52.5</v>
       </c>
       <c r="AO5" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2">
         <v>77.5</v>
@@ -1225,7 +1236,7 @@
         <v>58.4</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z6" s="2">
         <v>95.4</v>
@@ -1235,19 +1246,19 @@
         <v>74.5</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AD6" s="2">
         <v>68.900000000000006</v>
       </c>
       <c r="AE6" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF6" s="2">
         <v>70.3</v>
       </c>
       <c r="AG6" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH6" s="2">
         <v>97.8</v>
@@ -1257,22 +1268,22 @@
         <v>64.900000000000006</v>
       </c>
       <c r="AK6" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL6" s="2">
         <v>71.7</v>
       </c>
       <c r="AM6" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN6" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AO6" s="3"/>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41">
       <c r="A7" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2">
         <v>71.599999999999994</v>
@@ -1318,13 +1329,13 @@
         <v>68.099999999999994</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="X7" s="2">
         <v>43.6</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z7" s="2">
         <v>87.2</v>
@@ -1338,38 +1349,38 @@
         <v>69.2</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF7" s="2">
         <v>58.9</v>
       </c>
       <c r="AG7" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH7" s="2">
         <v>90.9</v>
       </c>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AK7" s="3"/>
       <c r="AL7" s="2">
         <v>63.5</v>
       </c>
       <c r="AM7" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN7" s="2">
         <v>54.4</v>
       </c>
       <c r="AO7" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41">
       <c r="A8" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2">
         <v>70.7</v>
@@ -1431,13 +1442,13 @@
         <v>72.400000000000006</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF8" s="2">
         <v>46.4</v>
       </c>
       <c r="AG8" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH8" s="2">
         <v>96.4</v>
@@ -1447,24 +1458,24 @@
         <v>85.5</v>
       </c>
       <c r="AK8" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL8" s="2">
         <v>62</v>
       </c>
       <c r="AM8" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN8" s="2">
         <v>57.1</v>
       </c>
       <c r="AO8" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41">
       <c r="A9" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2">
         <v>72.2</v>
@@ -1510,7 +1521,7 @@
         <v>63.8</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="X9" s="2">
         <v>54.1</v>
@@ -1532,7 +1543,7 @@
         <v>55.1</v>
       </c>
       <c r="AG9" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH9" s="2">
         <v>84.6</v>
@@ -1542,24 +1553,24 @@
         <v>87.2</v>
       </c>
       <c r="AK9" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL9" s="2">
         <v>57.2</v>
       </c>
       <c r="AM9" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN9" s="2">
         <v>43.1</v>
       </c>
       <c r="AO9" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41">
       <c r="A10" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2">
         <v>69.7</v>
@@ -1609,7 +1620,7 @@
         <v>40.700000000000003</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z10" s="2">
         <v>75.099999999999994</v>
@@ -1627,7 +1638,7 @@
         <v>54.3</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH10" s="2">
         <v>79.8</v>
@@ -1637,24 +1648,24 @@
         <v>60.7</v>
       </c>
       <c r="AK10" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL10" s="2">
         <v>70</v>
       </c>
       <c r="AM10" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN10" s="2">
         <v>52</v>
       </c>
       <c r="AO10" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41">
       <c r="A11" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2">
         <v>69.3</v>
@@ -1728,24 +1739,24 @@
         <v>65.8</v>
       </c>
       <c r="AK11" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL11" s="2">
         <v>44.9</v>
       </c>
       <c r="AM11" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN11" s="2">
         <v>42.7</v>
       </c>
       <c r="AO11" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B12" s="2">
         <v>69.599999999999994</v>
@@ -1795,7 +1806,7 @@
         <v>49.9</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z12" s="2">
         <v>72.599999999999994</v>
@@ -1813,7 +1824,7 @@
         <v>50.6</v>
       </c>
       <c r="AG12" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH12" s="2">
         <v>89.4</v>
@@ -1823,24 +1834,24 @@
         <v>70.8</v>
       </c>
       <c r="AK12" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL12" s="2">
         <v>63.8</v>
       </c>
       <c r="AM12" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN12" s="2">
         <v>56.3</v>
       </c>
       <c r="AO12" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41">
       <c r="A13" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B13" s="2">
         <v>70.099999999999994</v>
@@ -1918,18 +1929,18 @@
         <v>52.4</v>
       </c>
       <c r="AM13" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN13" s="2">
         <v>51</v>
       </c>
       <c r="AO13" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41">
       <c r="A14" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2">
         <v>70.400000000000006</v>
@@ -1979,7 +1990,7 @@
         <v>53</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z14" s="2">
         <v>78.3</v>
@@ -2005,24 +2016,24 @@
         <v>75</v>
       </c>
       <c r="AK14" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL14" s="2">
         <v>61.4</v>
       </c>
       <c r="AM14" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN14" s="2">
         <v>50.3</v>
       </c>
       <c r="AO14" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41">
       <c r="A15" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B15" s="2">
         <v>72.5</v>
@@ -2068,13 +2079,13 @@
         <v>61.8</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="X15" s="2">
         <v>50.6</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z15" s="2">
         <v>80.099999999999994</v>
@@ -2092,7 +2103,7 @@
         <v>45.6</v>
       </c>
       <c r="AG15" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH15" s="2">
         <v>104.2</v>
@@ -2106,18 +2117,18 @@
         <v>46.3</v>
       </c>
       <c r="AM15" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN15" s="2">
         <v>43.6</v>
       </c>
       <c r="AO15" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41">
       <c r="A16" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B16" s="2">
         <v>72.3</v>
@@ -2167,7 +2178,7 @@
         <v>46.2</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z16" s="2">
         <v>86.9</v>
@@ -2181,7 +2192,7 @@
         <v>68.2</v>
       </c>
       <c r="AE16" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF16" s="2">
         <v>56</v>
@@ -2199,18 +2210,18 @@
         <v>67</v>
       </c>
       <c r="AM16" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN16" s="2">
         <v>46.1</v>
       </c>
       <c r="AO16" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:41">
       <c r="A17" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B17" s="2">
         <v>72.2</v>
@@ -2260,7 +2271,7 @@
         <v>69</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z17" s="2">
         <v>89.7</v>
@@ -2270,19 +2281,19 @@
         <v>69.8</v>
       </c>
       <c r="AC17" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AD17" s="2">
         <v>75.900000000000006</v>
       </c>
       <c r="AE17" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF17" s="2">
         <v>48.8</v>
       </c>
       <c r="AG17" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH17" s="2">
         <v>114.2</v>
@@ -2296,18 +2307,18 @@
         <v>65.7</v>
       </c>
       <c r="AM17" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN17" s="2">
         <v>53</v>
       </c>
       <c r="AO17" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:41">
       <c r="A18" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B18" s="2">
         <v>73.400000000000006</v>
@@ -2353,13 +2364,13 @@
         <v>73.900000000000006</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="X18" s="2">
         <v>52.2</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z18" s="2">
         <v>97.9</v>
@@ -2373,13 +2384,13 @@
         <v>79.2</v>
       </c>
       <c r="AE18" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF18" s="2">
         <v>57.3</v>
       </c>
       <c r="AG18" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH18" s="2">
         <v>119.2</v>
@@ -2393,18 +2404,18 @@
         <v>68.099999999999994</v>
       </c>
       <c r="AM18" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN18" s="2">
         <v>52.7</v>
       </c>
       <c r="AO18" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:41">
       <c r="A19" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B19" s="2">
         <v>72</v>
@@ -2466,13 +2477,13 @@
         <v>74.2</v>
       </c>
       <c r="AE19" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF19" s="2">
         <v>58.3</v>
       </c>
       <c r="AG19" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH19" s="2">
         <v>122.9</v>
@@ -2486,18 +2497,18 @@
         <v>73.5</v>
       </c>
       <c r="AM19" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN19" s="2">
         <v>60.3</v>
       </c>
       <c r="AO19" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:41">
       <c r="A20" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B20" s="2">
         <v>75.3</v>
@@ -2571,24 +2582,24 @@
         <v>93.1</v>
       </c>
       <c r="AK20" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL20" s="2">
         <v>83.3</v>
       </c>
       <c r="AM20" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN20" s="2">
         <v>55.7</v>
       </c>
       <c r="AO20" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:41">
       <c r="A21" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B21" s="2">
         <v>73.5</v>
@@ -2634,13 +2645,13 @@
         <v>64.900000000000006</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="X21" s="2">
         <v>55.3</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z21" s="2">
         <v>108.1</v>
@@ -2658,7 +2669,7 @@
         <v>61.5</v>
       </c>
       <c r="AG21" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH21" s="2">
         <v>129.30000000000001</v>
@@ -2668,24 +2679,24 @@
         <v>100</v>
       </c>
       <c r="AK21" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL21" s="2">
         <v>78.73</v>
       </c>
       <c r="AM21" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN21" s="2">
         <v>59</v>
       </c>
       <c r="AO21" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:41">
       <c r="A22" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B22" s="2">
         <v>74.599999999999994</v>
@@ -2735,7 +2746,7 @@
         <v>69.599999999999994</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z22" s="2">
         <v>104.4</v>
@@ -2749,13 +2760,13 @@
         <v>92.5</v>
       </c>
       <c r="AE22" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF22" s="2">
         <v>60.8</v>
       </c>
       <c r="AG22" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH22" s="2">
         <v>133.1</v>
@@ -2769,18 +2780,18 @@
         <v>53.3</v>
       </c>
       <c r="AM22" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN22" s="2">
         <v>60</v>
       </c>
       <c r="AO22" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:41">
       <c r="A23" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B23" s="2">
         <v>77.7</v>
@@ -2830,7 +2841,7 @@
         <v>66</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z23" s="2">
         <v>106.9</v>
@@ -2844,13 +2855,13 @@
         <v>93.8</v>
       </c>
       <c r="AE23" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF23" s="2">
         <v>76.900000000000006</v>
       </c>
       <c r="AG23" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH23" s="2">
         <v>132.69999999999999</v>
@@ -2864,18 +2875,18 @@
         <v>109.5</v>
       </c>
       <c r="AM23" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN23" s="2">
         <v>61.2</v>
       </c>
       <c r="AO23" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:41">
       <c r="A24" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B24" s="2">
         <v>80.099999999999994</v>
@@ -2941,7 +2952,7 @@
         <v>68.599999999999994</v>
       </c>
       <c r="AG24" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH24" s="2">
         <v>135.9</v>
@@ -2951,24 +2962,24 @@
         <v>98</v>
       </c>
       <c r="AK24" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL24" s="2">
         <v>75.099999999999994</v>
       </c>
       <c r="AM24" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN24" s="2">
         <v>87.9</v>
       </c>
       <c r="AO24" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:41">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B25" s="2">
         <v>83.7</v>
@@ -3018,7 +3029,7 @@
         <v>87.7</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z25" s="2">
         <v>129.9</v>
@@ -3032,13 +3043,13 @@
         <v>90.8</v>
       </c>
       <c r="AE25" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF25" s="2">
         <v>71.3</v>
       </c>
       <c r="AG25" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH25" s="2">
         <v>133.9</v>
@@ -3048,24 +3059,24 @@
         <v>105.8</v>
       </c>
       <c r="AK25" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL25" s="2">
         <v>101.7</v>
       </c>
       <c r="AM25" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN25" s="2">
         <v>87</v>
       </c>
       <c r="AO25" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:41">
       <c r="A26" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B26" s="2">
         <v>85.7</v>
@@ -3111,13 +3122,13 @@
         <v>83.2</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="X26" s="2">
         <v>68.2</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z26" s="2">
         <v>124.2</v>
@@ -3127,19 +3138,19 @@
         <v>111.6</v>
       </c>
       <c r="AC26" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AD26" s="2">
         <v>89.9</v>
       </c>
       <c r="AE26" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF26" s="2">
         <v>77.5</v>
       </c>
       <c r="AG26" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH26" s="2">
         <v>135.5</v>
@@ -3153,16 +3164,16 @@
         <v>83.2</v>
       </c>
       <c r="AM26" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN26" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AO26" s="3"/>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:41">
       <c r="A27" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B27" s="2">
         <v>90.5</v>
@@ -3224,13 +3235,13 @@
         <v>98.4</v>
       </c>
       <c r="AE27" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF27" s="2">
         <v>89.8</v>
       </c>
       <c r="AG27" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH27" s="2">
         <v>141.4</v>
@@ -3244,18 +3255,18 @@
         <v>108.1</v>
       </c>
       <c r="AM27" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN27" s="2">
         <v>75.3</v>
       </c>
       <c r="AO27" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:41">
       <c r="A28" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B28" s="2">
         <v>93.2</v>
@@ -3317,7 +3328,7 @@
         <v>111</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF28" s="2">
         <v>77.099999999999994</v>
@@ -3331,24 +3342,24 @@
         <v>114.5</v>
       </c>
       <c r="AK28" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL28" s="2">
         <v>94.3</v>
       </c>
       <c r="AM28" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN28" s="2">
         <v>69.900000000000006</v>
       </c>
       <c r="AO28" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:41">
       <c r="A29" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B29" s="2">
         <v>105</v>
@@ -3410,7 +3421,7 @@
         <v>122</v>
       </c>
       <c r="AE29" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF29" s="2">
         <v>90.4</v>
@@ -3424,24 +3435,24 @@
         <v>128.69999999999999</v>
       </c>
       <c r="AK29" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL29" s="2">
         <v>109.7</v>
       </c>
       <c r="AM29" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN29" s="2">
         <v>102.1</v>
       </c>
       <c r="AO29" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:41">
       <c r="A30" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B30" s="2">
         <v>114.4</v>
@@ -3487,7 +3498,7 @@
         <v>100.9</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="X30" s="2">
         <v>78.400000000000006</v>
@@ -3517,24 +3528,24 @@
         <v>121.5</v>
       </c>
       <c r="AK30" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL30" s="2">
         <v>128.1</v>
       </c>
       <c r="AM30" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN30" s="2">
         <v>82.4</v>
       </c>
       <c r="AO30" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:41">
       <c r="A31" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B31" s="2">
         <v>125.9</v>
@@ -3580,7 +3591,7 @@
         <v>117.8</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="X31" s="2">
         <v>112.9</v>
@@ -3594,7 +3605,7 @@
         <v>140.4</v>
       </c>
       <c r="AC31" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AD31" s="2">
         <v>136.6</v>
@@ -3604,7 +3615,7 @@
         <v>120.1</v>
       </c>
       <c r="AG31" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH31" s="2">
         <v>186.8</v>
@@ -3614,24 +3625,24 @@
         <v>151.4</v>
       </c>
       <c r="AK31" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL31" s="2">
         <v>100</v>
       </c>
       <c r="AM31" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN31" s="2">
         <v>96.3</v>
       </c>
       <c r="AO31" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:41">
       <c r="A32" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B32" s="2">
         <v>130</v>
@@ -3705,24 +3716,24 @@
         <v>160.1</v>
       </c>
       <c r="AK32" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL32" s="2">
         <v>90.5</v>
       </c>
       <c r="AM32" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN32" s="2">
         <v>124.2</v>
       </c>
       <c r="AO32" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:41">
       <c r="A33" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B33" s="2">
         <v>139.9</v>
@@ -3768,7 +3779,7 @@
         <v>125</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="X33" s="2">
         <v>124.4</v>
@@ -3786,7 +3797,7 @@
         <v>135.30000000000001</v>
       </c>
       <c r="AE33" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF33" s="2">
         <v>119.8</v>
@@ -3804,18 +3815,18 @@
         <v>132.19999999999999</v>
       </c>
       <c r="AM33" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN33" s="2">
         <v>119.3</v>
       </c>
       <c r="AO33" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:41">
       <c r="A34" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B34" s="2">
         <v>141.1</v>
@@ -3861,13 +3872,13 @@
         <v>134.19999999999999</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="X34" s="2">
         <v>110.8</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z34" s="2">
         <v>171.4</v>
@@ -3881,7 +3892,7 @@
         <v>168.2</v>
       </c>
       <c r="AE34" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF34" s="2">
         <v>124.5</v>
@@ -3899,16 +3910,17 @@
         <v>125.2</v>
       </c>
       <c r="AM34" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN34" s="2">
         <v>113.2</v>
       </c>
       <c r="AO34" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>